--- a/InputData/trans/SoCDTtiNTY/Share of Cargo Dist Transported that is New This Year.xlsx
+++ b/InputData/trans/SoCDTtiNTY/Share of Cargo Dist Transported that is New This Year.xlsx
@@ -1,26 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rorvis\Dropbox (Energy InNovation)\My Documents\Energy Policy Solutions\Hong Kong\Models\eps-hongkong\InputData\trans\SoCDTtiNTY\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\daiyang.zhang\Desktop\eps-HK-3.4.9-working\InputData\trans\SoCDTtiNTY\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E93C423-87EE-4C3A-AA53-6BA818892054}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="360" yWindow="105" windowWidth="21075" windowHeight="10050" activeTab="1"/>
+    <workbookView xWindow="-450" yWindow="0" windowWidth="16480" windowHeight="10200" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
-    <sheet name="SoCDTtiNTY" sheetId="2" r:id="rId2"/>
+    <sheet name="SoCDTtiNTY-psgr" sheetId="2" r:id="rId2"/>
+    <sheet name="SoCDTtiNTY-frgt" sheetId="4" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="145621" calcOnSave="0"/>
+  <externalReferences>
+    <externalReference r:id="rId4"/>
+  </externalReferences>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="26">
   <si>
     <t>SoCDTtiNTY Share of Cargo Dist Transported that is New This Year</t>
   </si>
@@ -76,16 +92,34 @@
     <t>motorbikes</t>
   </si>
   <si>
-    <t>passenger</t>
-  </si>
-  <si>
-    <t>freight</t>
+    <t>Share that is New (dimensionless)</t>
+  </si>
+  <si>
+    <t>battery electric vehicle</t>
+  </si>
+  <si>
+    <t>natural gas vehicle</t>
+  </si>
+  <si>
+    <t>gasoline vehicle</t>
+  </si>
+  <si>
+    <t>diesel vehicle</t>
+  </si>
+  <si>
+    <t>plugin hybrid vehicle</t>
+  </si>
+  <si>
+    <t>LPG vehicle</t>
+  </si>
+  <si>
+    <t>hydrogen vehicle</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -123,11 +157,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -146,10 +186,83 @@
 </styleSheet>
 </file>
 
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="About"/>
+      <sheetName val="HK"/>
+      <sheetName val="Data"/>
+      <sheetName val="NTS 1-20"/>
+      <sheetName val="AVL"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4">
+        <row r="2">
+          <cell r="B2">
+            <v>8</v>
+          </cell>
+          <cell r="C2">
+            <v>8</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="B3">
+            <v>10</v>
+          </cell>
+          <cell r="C3">
+            <v>10</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="B4">
+            <v>24</v>
+          </cell>
+          <cell r="C4">
+            <v>24</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="B5">
+            <v>23</v>
+          </cell>
+          <cell r="C5">
+            <v>23</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="B6">
+            <v>32</v>
+          </cell>
+          <cell r="C6">
+            <v>32</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="B7">
+            <v>7</v>
+          </cell>
+          <cell r="C7">
+            <v>12</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -187,9 +300,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -224,7 +337,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -259,7 +372,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -432,16 +545,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -449,47 +562,47 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>11</v>
       </c>
@@ -500,90 +613,480 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <tabColor theme="3"/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="12.85546875" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="1" max="1" width="19.1796875" customWidth="1"/>
+    <col min="2" max="8" width="14.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="B1" s="2" t="s">
+    <row r="1" spans="1:8" s="4" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>12</v>
       </c>
       <c r="B2">
-        <v>8.1500000000000003E-2</v>
+        <f>1/[1]AVL!B2</f>
+        <v>0.125</v>
       </c>
       <c r="C2">
-        <v>8.3000000000000004E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+        <f>B2</f>
+        <v>0.125</v>
+      </c>
+      <c r="D2">
+        <f t="shared" ref="D2:H2" si="0">C2</f>
+        <v>0.125</v>
+      </c>
+      <c r="E2">
+        <f t="shared" si="0"/>
+        <v>0.125</v>
+      </c>
+      <c r="F2">
+        <f t="shared" si="0"/>
+        <v>0.125</v>
+      </c>
+      <c r="G2">
+        <f t="shared" si="0"/>
+        <v>0.125</v>
+      </c>
+      <c r="H2">
+        <f t="shared" si="0"/>
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>13</v>
       </c>
       <c r="B3">
-        <v>6.5000000000000002E-2</v>
+        <f>1/[1]AVL!B3</f>
+        <v>0.1</v>
       </c>
       <c r="C3">
-        <v>6.6000000000000003E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+        <f t="shared" ref="C3:H7" si="1">B3</f>
+        <v>0.1</v>
+      </c>
+      <c r="D3">
+        <f t="shared" si="1"/>
+        <v>0.1</v>
+      </c>
+      <c r="E3">
+        <f t="shared" si="1"/>
+        <v>0.1</v>
+      </c>
+      <c r="F3">
+        <f t="shared" si="1"/>
+        <v>0.1</v>
+      </c>
+      <c r="G3">
+        <f t="shared" si="1"/>
+        <v>0.1</v>
+      </c>
+      <c r="H3">
+        <f t="shared" si="1"/>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>14</v>
       </c>
       <c r="B4">
-        <v>4.1599999999999998E-2</v>
+        <f>1/[1]AVL!B4</f>
+        <v>4.1666666666666664E-2</v>
       </c>
       <c r="C4">
-        <v>4.2500000000000003E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="D4">
+        <f t="shared" si="1"/>
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="1"/>
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="1"/>
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="G4">
+        <f t="shared" si="1"/>
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="H4">
+        <f t="shared" si="1"/>
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>15</v>
       </c>
       <c r="B5">
-        <v>4.2999999999999997E-2</v>
+        <f>1/[1]AVL!B5</f>
+        <v>4.3478260869565216E-2</v>
       </c>
       <c r="C5">
-        <v>2.9000000000000001E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>4.3478260869565216E-2</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="1"/>
+        <v>4.3478260869565216E-2</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="1"/>
+        <v>4.3478260869565216E-2</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="1"/>
+        <v>4.3478260869565216E-2</v>
+      </c>
+      <c r="G5">
+        <f t="shared" si="1"/>
+        <v>4.3478260869565216E-2</v>
+      </c>
+      <c r="H5">
+        <f t="shared" si="1"/>
+        <v>4.3478260869565216E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>16</v>
       </c>
       <c r="B6">
-        <v>2.9819999999999999E-2</v>
+        <f>1/[1]AVL!B6</f>
+        <v>3.125E-2</v>
       </c>
       <c r="C6">
-        <v>3.0300000000000001E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+        <f t="shared" si="1"/>
+        <v>3.125E-2</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="1"/>
+        <v>3.125E-2</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="1"/>
+        <v>3.125E-2</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="1"/>
+        <v>3.125E-2</v>
+      </c>
+      <c r="G6">
+        <f t="shared" si="1"/>
+        <v>3.125E-2</v>
+      </c>
+      <c r="H6">
+        <f t="shared" si="1"/>
+        <v>3.125E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>17</v>
       </c>
       <c r="B7">
-        <v>0.14000000000000001</v>
+        <f>1/[1]AVL!B7</f>
+        <v>0.14285714285714285</v>
       </c>
       <c r="C7">
-        <v>8.2500000000000004E-2</v>
+        <f t="shared" si="1"/>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="1"/>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="1"/>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="1"/>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="G7">
+        <f t="shared" si="1"/>
+        <v>0.14285714285714285</v>
+      </c>
+      <c r="H7">
+        <f t="shared" si="1"/>
+        <v>0.14285714285714285</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+  <sheetPr>
+    <tabColor theme="3"/>
+  </sheetPr>
+  <dimension ref="A1:H7"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="19.1796875" customWidth="1"/>
+    <col min="2" max="8" width="14.453125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8" s="4" customFormat="1" ht="29" x14ac:dyDescent="0.35">
+      <c r="A1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B2">
+        <f>1/[1]AVL!C2</f>
+        <v>0.125</v>
+      </c>
+      <c r="C2">
+        <f>B2</f>
+        <v>0.125</v>
+      </c>
+      <c r="D2">
+        <f t="shared" ref="D2:H2" si="0">C2</f>
+        <v>0.125</v>
+      </c>
+      <c r="E2">
+        <f t="shared" si="0"/>
+        <v>0.125</v>
+      </c>
+      <c r="F2">
+        <f t="shared" si="0"/>
+        <v>0.125</v>
+      </c>
+      <c r="G2">
+        <f t="shared" si="0"/>
+        <v>0.125</v>
+      </c>
+      <c r="H2">
+        <f t="shared" si="0"/>
+        <v>0.125</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B3">
+        <f>1/[1]AVL!C3</f>
+        <v>0.1</v>
+      </c>
+      <c r="C3">
+        <f t="shared" ref="C3:H7" si="1">B3</f>
+        <v>0.1</v>
+      </c>
+      <c r="D3">
+        <f t="shared" si="1"/>
+        <v>0.1</v>
+      </c>
+      <c r="E3">
+        <f t="shared" si="1"/>
+        <v>0.1</v>
+      </c>
+      <c r="F3">
+        <f t="shared" si="1"/>
+        <v>0.1</v>
+      </c>
+      <c r="G3">
+        <f t="shared" si="1"/>
+        <v>0.1</v>
+      </c>
+      <c r="H3">
+        <f t="shared" si="1"/>
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4">
+        <f>1/[1]AVL!C4</f>
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="C4">
+        <f t="shared" si="1"/>
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="D4">
+        <f t="shared" si="1"/>
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="1"/>
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="F4">
+        <f t="shared" si="1"/>
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="G4">
+        <f t="shared" si="1"/>
+        <v>4.1666666666666664E-2</v>
+      </c>
+      <c r="H4">
+        <f t="shared" si="1"/>
+        <v>4.1666666666666664E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5">
+        <f>1/[1]AVL!C5</f>
+        <v>4.3478260869565216E-2</v>
+      </c>
+      <c r="C5">
+        <f t="shared" si="1"/>
+        <v>4.3478260869565216E-2</v>
+      </c>
+      <c r="D5">
+        <f t="shared" si="1"/>
+        <v>4.3478260869565216E-2</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="1"/>
+        <v>4.3478260869565216E-2</v>
+      </c>
+      <c r="F5">
+        <f t="shared" si="1"/>
+        <v>4.3478260869565216E-2</v>
+      </c>
+      <c r="G5">
+        <f t="shared" si="1"/>
+        <v>4.3478260869565216E-2</v>
+      </c>
+      <c r="H5">
+        <f t="shared" si="1"/>
+        <v>4.3478260869565216E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6">
+        <f>1/[1]AVL!C6</f>
+        <v>3.125E-2</v>
+      </c>
+      <c r="C6">
+        <f t="shared" si="1"/>
+        <v>3.125E-2</v>
+      </c>
+      <c r="D6">
+        <f t="shared" si="1"/>
+        <v>3.125E-2</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="1"/>
+        <v>3.125E-2</v>
+      </c>
+      <c r="F6">
+        <f t="shared" si="1"/>
+        <v>3.125E-2</v>
+      </c>
+      <c r="G6">
+        <f t="shared" si="1"/>
+        <v>3.125E-2</v>
+      </c>
+      <c r="H6">
+        <f t="shared" si="1"/>
+        <v>3.125E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7">
+        <f>1/[1]AVL!C7</f>
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="C7">
+        <f t="shared" si="1"/>
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="D7">
+        <f t="shared" si="1"/>
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="1"/>
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="F7">
+        <f t="shared" si="1"/>
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="G7">
+        <f t="shared" si="1"/>
+        <v>8.3333333333333329E-2</v>
+      </c>
+      <c r="H7">
+        <f t="shared" si="1"/>
+        <v>8.3333333333333329E-2</v>
       </c>
     </row>
   </sheetData>
@@ -592,40 +1095,41 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010095990DC6317597479C114DD4E6AB1F33" ma:contentTypeVersion="14" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="00c0eb7d4c43453177323eb1ac58d7e7">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="7889d872-e2a2-4afb-87bc-97561eced75f" xmlns:ns3="c9df191c-55f2-496b-9838-9a5abe4742ad" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="b5fe72540fcc493259a136614ad94e00" ns1:_="" ns2:_="" ns3:_="">
-    <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
-    <xsd:import namespace="7889d872-e2a2-4afb-87bc-97561eced75f"/>
-    <xsd:import namespace="c9df191c-55f2-496b-9838-9a5abe4742ad"/>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D257B2780BAD0A45A02FA065B9C6CC6A" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="54b727ac31dab95898e9cf92f0402afe">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cb176f07-3112-4ee9-93fd-ae2cb5f3e433" xmlns:ns3="6b15a3a4-8173-42d6-9deb-398ec38eca4b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="42611c3eb46fef4c2b2610d1e51cc1b0" ns2:_="" ns3:_="">
+    <xsd:import namespace="cb176f07-3112-4ee9-93fd-ae2cb5f3e433"/>
+    <xsd:import namespace="6b15a3a4-8173-42d6-9deb-398ec38eca4b"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
           <xsd:element name="documentManagement">
             <xsd:complexType>
               <xsd:all>
-                <xsd:element ref="ns2:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns2:SharedWithDetails" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceAutoTags" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceLocation" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceGenerationTime" minOccurs="0"/>
-                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyProperties" minOccurs="0"/>
-                <xsd:element ref="ns1:_ip_UnifiedCompliancePolicyUIAction" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns3:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -633,24 +1137,85 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="http://schemas.microsoft.com/sharepoint/v3" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="cb176f07-3112-4ee9-93fd-ae2cb5f3e433" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="_ip_UnifiedCompliancePolicyProperties" ma:index="18" nillable="true" ma:displayName="Unified Compliance Policy Properties" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyProperties">
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="_ip_UnifiedCompliancePolicyUIAction" ma:index="19" nillable="true" ma:displayName="Unified Compliance Policy UI Action" ma:hidden="true" ma:internalName="_ip_UnifiedCompliancePolicyUIAction">
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="12" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="13" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="14" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="18" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="19" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="22" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="ca0deac2-43b9-460d-a4eb-012f87ec990e" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="7889d872-e2a2-4afb-87bc-97561eced75f" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="6b15a3a4-8173-42d6-9deb-398ec38eca4b" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="8" nillable="true" ma:displayName="Shared With" ma:description="" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="SharedWithUsers" ma:index="10" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
       <xsd:complexType>
         <xsd:complexContent>
           <xsd:extension base="dms:UserMulti">
@@ -669,70 +1234,23 @@
         </xsd:complexContent>
       </xsd:complexType>
     </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="9" nillable="true" ma:displayName="Shared With Details" ma:description="" ma:internalName="SharedWithDetails" ma:readOnly="true">
+    <xsd:element name="SharedWithDetails" ma:index="11" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
-  </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="c9df191c-55f2-496b-9838-9a5abe4742ad" elementFormDefault="qualified">
-    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="MediaServiceMetadata" ma:index="10" nillable="true" ma:displayName="MediaServiceMetadata" ma:description="" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceFastMetadata" ma:index="11" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:description="" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:description="" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoTags" ma:index="13" nillable="true" ma:displayName="MediaServiceAutoTags" ma:description="" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceLocation" ma:index="14" nillable="true" ma:displayName="MediaServiceLocation" ma:description="" ma:internalName="MediaServiceLocation" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="15" nillable="true" ma:displayName="MediaServiceOCR" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="17" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="20" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="21" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
+    <xsd:element name="TaxCatchAll" ma:index="23" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{caf201a3-c970-477d-b8ee-c5923cb026e5}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="6b15a3a4-8173-42d6-9deb-398ec38eca4b">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
@@ -834,35 +1352,23 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{864B9C6F-8A1E-4D6D-AC05-ADAD8ADF2231}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{E99E059C-6C8D-45E1-B391-420FC2DAE855}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1542D730-DB3B-42B6-ACDB-E0C050AF4211}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1CA52D22-F5A4-4B2A-92DB-4296E24AF77C}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
     <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="7889d872-e2a2-4afb-87bc-97561eced75f"/>
-    <ds:schemaRef ds:uri="c9df191c-55f2-496b-9838-9a5abe4742ad"/>
+    <ds:schemaRef ds:uri="cb176f07-3112-4ee9-93fd-ae2cb5f3e433"/>
+    <ds:schemaRef ds:uri="6b15a3a4-8173-42d6-9deb-398ec38eca4b"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
@@ -871,12 +1377,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1F5F6882-0789-423C-9D51-7FE368DB3B77}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>